--- a/ig/DM-OCTOBRE-2024/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2024/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="403">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -457,7 +457,13 @@
     <t>241</t>
   </si>
   <si>
-    <t>Foyer d'action éducative (FAE)</t>
+    <t>Établissement de Placement</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>Service d'Activité de Jour</t>
   </si>
   <si>
     <t>246</t>
@@ -778,12 +784,6 @@
     <t>Service médico-psychologique régional (SMPR)</t>
   </si>
   <si>
-    <t>418</t>
-  </si>
-  <si>
-    <t>Service d'enquêtes sociales (SES)</t>
-  </si>
-  <si>
     <t>422</t>
   </si>
   <si>
@@ -802,12 +802,6 @@
     <t>Syndicat inter hospitalier (SIH)</t>
   </si>
   <si>
-    <t>427</t>
-  </si>
-  <si>
-    <t>Service éducatif auprès des tribunaux (SEAT)</t>
-  </si>
-  <si>
     <t>430</t>
   </si>
   <si>
@@ -847,13 +841,13 @@
     <t>440</t>
   </si>
   <si>
-    <t>Service d'investigation et d'orientation éducative (SIOE)</t>
+    <t>Service d'Investigation Educative</t>
   </si>
   <si>
     <t>441</t>
   </si>
   <si>
-    <t>Centre d'action éducative (CAE)</t>
+    <t>Service d'Intervention Educative en Milieu Ouvert</t>
   </si>
   <si>
     <t>442</t>
@@ -898,12 +892,6 @@
     <t>Etablissement d'Accueil Non Médicalisé pour personnes handicapées</t>
   </si>
   <si>
-    <t>453</t>
-  </si>
-  <si>
-    <t>Service de réparation pénale</t>
-  </si>
-  <si>
     <t>460</t>
   </si>
   <si>
@@ -919,7 +907,7 @@
     <t>462</t>
   </si>
   <si>
-    <t>Lieux de vie</t>
+    <t>Lieux de Vie et d'Accueil</t>
   </si>
   <si>
     <t>463</t>
@@ -1141,7 +1129,7 @@
     <t>646</t>
   </si>
   <si>
-    <t>Centre de Vaccination International</t>
+    <t>Centre de Vaccination Internationale</t>
   </si>
   <si>
     <t>647</t>
@@ -1150,6 +1138,12 @@
     <t>Equipe de Soins Spécialisés</t>
   </si>
   <si>
+    <t>648</t>
+  </si>
+  <si>
+    <t>Structure qui contribue au Service d'Accès aux Soins</t>
+  </si>
+  <si>
     <t>695</t>
   </si>
   <si>
@@ -1184,6 +1178,18 @@
   </si>
   <si>
     <t>Maison sport-santé</t>
+  </si>
+  <si>
+    <t>701</t>
+  </si>
+  <si>
+    <t>Maison des adolescents (MDA)</t>
+  </si>
+  <si>
+    <t>702</t>
+  </si>
+  <si>
+    <t>Point Accueil Ecoute Jeunes (PAEJ)</t>
   </si>
   <si>
     <t/>
@@ -1486,7 +1492,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B183"/>
+  <dimension ref="A1:B184"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2946,15 +2952,23 @@
         <v>390</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>392</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -2981,7 +2995,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>43</v>
@@ -2989,42 +3003,42 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
